--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/05 16:45:05</t>
+          <t>09/14 10:05:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/05 19:09:07</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6250</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>12345.68</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6250</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>12345.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/14 11:46:55</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12345.68</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12345.68</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/14 10:05:56</t>
+          <t>09/15 10:26:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/14 11:46:55</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>170000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>20481.93</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12345</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.68</t>
+          <t>20481.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/15 11:34:57</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20481</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>170000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>170000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20481.93</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20481</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20481.93</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/15 12:39:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>145000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>17682.93</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/15 10:26:40</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>170000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>20481.93</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/15 11:34:57</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>20481</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>170000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>315000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>38164.85</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20481</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.93</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>17683.85</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/15 13:40:08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>17683</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/15 11:34:57</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>20481</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>315000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38164.85</t>
+          <t>315000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>38164.85</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>38164</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>17683.85</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.85</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/15 12:39:33</t>
+          <t>09/17 09:12:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17682.93</t>
+          <t>14337.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/15 10:26:40</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>170000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>20481.93</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/15 13:40:08</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>17683</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/15 11:34:57</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20481</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>119000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14337.35</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>315000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>38164.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>38164</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.85</t>
+          <t>14337.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/17 11:07:52</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14337</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>119000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14337.35</t>
+          <t>119000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14337.35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14337</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>14337.35</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -72,213 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/17 09:12:01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>119000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>14337.35</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17 11:07:52</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>14337</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14337.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>14337</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.35</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/18 11:54:55</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12500</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12500</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/18 13:10:40</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12500</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 11:54:55</t>
+          <t>09/20 11:57:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/18 13:10:40</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12500</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>23529.41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12500</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>23529.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/20 11:57:21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23529.41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>23529.41</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22241.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/20 13:44:44</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>23529</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/20 11:57:21</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1288</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>23529.41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>24817</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>22241.41</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-1287.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 11:57:16</t>
+          <t>09/21 11:45:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>34146.34</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/20 13:44:44</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>23529</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 11:57:21</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>280000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>34146.34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23529.41</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>24817</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>-1287.59</t>
+          <t>34146.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/21 13:00:19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>34146</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>280000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>34146.34</t>
+          <t>280000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34146.34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>34146</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>34146.34</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21 11:45:13</t>
+          <t>09/22 19:10:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34146.34</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/21 13:00:19</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>34146</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>34146.34</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>34146</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.34</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22 19:10:06</t>
+          <t>09/22 19:10:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/22 19:10:38</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12048.19</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11516.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/22 19:12:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/22 19:10:38</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5388</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11516.76</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6516.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/22 19:12:36</t>
+          <t>09/22 20:39:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -229,83 +229,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/22 19:12:36</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/22 19:10:38</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6516.76</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22 19:10:33</t>
+          <t>09/23 12:36:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>13253.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,140 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/22 20:39:22</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6516</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/22 19:12:36</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/22 19:10:38</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>110000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13253.01</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11904.76</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.76</t>
+          <t>13253.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/23 13:36:04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20858.9</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/23 12:36:35</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>13253.01</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>280000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34111.91</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13253.01</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>34111.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/23 14:47:45</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>34111</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>280000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>34111.91</t>
+          <t>280000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34111.91</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>34111</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>34111.91</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/24 10:57:23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5736.1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5736.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5736.1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5736.1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5736.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,30 +199,45 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/24 12:43:14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5736</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>5736.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -234,24 +249,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5736.1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5736</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5736.1</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 10:57:23</t>
+          <t>09/27 10:34:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5736.1</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5736.1</t>
+          <t>19512.2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/24 12:43:14</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5736</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5736.1</t>
+          <t>19512.2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5736.1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5736</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.1</t>
+          <t>19512.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/27 12:32:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-1000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19512.2</t>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19512.2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19512.2</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20512.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/27 12:33:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20515</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/27 12:32:05</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>-1000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19512.2</t>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-1000</t>
+          <t>19512.2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19515</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>20512.2</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-2.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/27 10:34:47</t>
+          <t>09/28 14:39:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19512.2</t>
+          <t>32098.77</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/27 12:33:36</t>
+          <t>09/28 17:32:41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20515</t>
+          <t>32098</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -226,86 +226,59 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>09/27 12:32:05</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>-1000</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>260000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>32098.77</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19512.2</t>
+          <t>32098</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19515</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>-2.8</t>
+          <t>0.77</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 14:39:55</t>
+          <t>09/29 10:23:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32098.77</t>
+          <t>19875.78</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/28 17:32:41</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>32098</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>19875.78</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32098.77</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32098</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.77</t>
+          <t>19875.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/29 11:25:16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12269.94</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/29 10:23:35</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>160000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>19875.78</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19875.78</t>
+          <t>260000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32145.72</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19875.78</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>32145.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/29 12:49:43</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>32145</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>260000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32145.72</t>
+          <t>260000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32145.72</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>32145</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>32145.72</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 11:25:16</t>
+          <t>09/29 20:57:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>19161.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09/29 11:25:16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12269.94</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>09/29 10:23:35</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>160000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>19875.78</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/29 12:49:43</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>32145</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>260000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32145.72</t>
+          <t>420000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>32145</t>
+          <t>51307.39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>32145</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.72</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>19162.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/29 21:13:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/29 12:49:43</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>32145</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>420000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>51307.39</t>
+          <t>420000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>32145</t>
+          <t>51307.39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>32333</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>19162.39</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18974.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/29 21:13:01</t>
+          <t>09/29 23:23:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>18974</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -313,83 +313,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>09/29 21:13:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>09/29 12:49:43</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>32145</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>420000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>51307.39</t>
+          <t>420000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32333</t>
+          <t>51307.39</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>51307</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>18974.39</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/30 08:29:16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>130000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15757.58</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15757.58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15757.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/30 10:12:44</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>37037.04</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/30 08:29:16</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>130000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>15757.58</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15757.58</t>
+          <t>430000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52794.61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15757.58</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>52794.61</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 10:12:44</t>
+          <t>09/30 08:29:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>15757.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,186 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/30 08:29:16</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.25</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>15757.58</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>130000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>430000</t>
+          <t>15757.58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>52794.61</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>52794.61</t>
+          <t>15757.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/30 10:14:16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36809.82</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/30 08:29:16</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>130000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>15757.58</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15757.58</t>
+          <t>430000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52567.39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15757.58</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>52567.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/30 11:36:33</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>52567</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>430000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>52567.39</t>
+          <t>430000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52567.39</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>52567</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>52567.39</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 10:14:16</t>
+          <t>09/30 18:35:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09/30 10:14:16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>36809.82</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>09/30 08:29:16</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>130000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>15757.58</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/30 11:36:33</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>52567</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>430000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>52567.39</t>
+          <t>563000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>52567</t>
+          <t>69192.39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>52567</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.39</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>16625.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 18:35:00</t>
+          <t>09/30 10:14:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/30 10:14:16</t>
+          <t>09/30 08:29:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>15757.58</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -156,213 +156,171 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>09/30 08:29:16</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8.25</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>15757.58</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>09/30 11:36:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>52567</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>标记人</t>
+          <t/>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>操作人</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>09/30 11:36:33</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>52567</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>430000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>563000</t>
+          <t>52567.39</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>69192.39</t>
+          <t>52567</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>52567</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>16625.39</t>
+          <t>0.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 10:14:16</t>
+          <t>09/30 18:36:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>16521.74</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09/30 10:14:16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>36809.82</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>09/30 08:29:16</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>130000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>15757.58</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/30 11:36:33</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>52567</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>430000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>52567.39</t>
+          <t>563000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>52567</t>
+          <t>69089.13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>52567</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.39</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>16522.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/30 18:40:35</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/30 11:36:33</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>52567</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>563000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>69089.13</t>
+          <t>563000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>52567</t>
+          <t>69089.13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>53567</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>16522.13</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>15522.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/30 18:40:35</t>
+          <t>09/30 19:28:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -313,83 +313,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>09/30 18:40:35</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>09/30 11:36:33</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>52567</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>563000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>69089.13</t>
+          <t>563000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>53567</t>
+          <t>69089.13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>69089</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>15522.13</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/01 18:22:09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12269.94</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12269.94</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/01 14:45:15</t>
+          <t>10/02 09:46:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/01 18:22:09</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12269</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>32997</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>3882</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12269</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.94</t>
+          <t>3882</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/02 18:18:37</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3882</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>32997</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>32997</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3882</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3882</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3882</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/02 09:46:37</t>
+          <t>10/04 11:11:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>26744.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/02 18:18:37</t>
+          <t>10/04 15:30:09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>25856</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -226,59 +226,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/04 11:11:04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>32997</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>26744.19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>26744</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/04 11:11:01</t>
+          <t>10/06 10:19:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26744.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/04 15:30:09</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>25856</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/04 11:11:04</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26744.19</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>26744</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.19</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/06 12:41:15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9523.81</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/06 10:19:47</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>11904.76</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>180000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21428.57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21428.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/06 12:41:19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>180000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>180000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21428.57</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21428.57</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21140.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>10/06 15:01:35</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>21140</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>10/06 12:41:19</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>180000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21428.57</t>
+          <t>180000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>21428.57</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21428</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21140.57</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/06 12:41:15</t>
+          <t>10/07 12:39:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9523.81</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/06 10:19:47</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>11904.76</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/06 15:01:35</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>21140</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/06 12:41:19</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>180000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21428.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21428</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.57</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/07 14:22:08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>36144</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>36144</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>36144.58</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/07 15:28:25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>93023.26</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/07 12:39:46</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/07 14:22:08</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>36144</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>1100000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>129167.83</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>36144</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.58</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>93023.83</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>10/07 15:28:44</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>10/07 14:22:08</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>36144</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>129167.83</t>
+          <t>1100000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>129167.83</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>36732</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>93023.83</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>92435.83</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/07 15:28:44</t>
+          <t>10/07 18:44:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>92435</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -259,7 +259,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -271,83 +271,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>10/07 15:28:44</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>10/07 14:22:08</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>36144</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>129167.83</t>
+          <t>1100000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>129167.83</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>129167</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>92435.83</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.83</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/07 15:28:25</t>
+          <t>10/09 11:01:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>93023.26</t>
+          <t>14457.83</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,267 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/07 12:39:46</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>36144.58</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/07 18:44:02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>92435</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/07 15:28:44</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
+          <t>120000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/07 14:22:08</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36144</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>14457.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1100000</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>129167.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>129167</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0.83</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14457.83</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/09 11:02:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>120000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14457.83</t>
+          <t>120000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14457.83</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>14457.83</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14269.83</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10/09 14:17:06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14269</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/09 11:02:01</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>120000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14457.83</t>
+          <t>120000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>14457.83</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14457</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>14269.83</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.83</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/09 11:01:52</t>
+          <t>10/11 10:00:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14457.83</t>
+          <t>6024.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/09 14:17:06</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>14269</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/09 11:02:01</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6024.1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14457.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>14457</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.83</t>
+          <t>6024.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/11 10:01:04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6024.1</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6024.1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6024.1</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5736.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10/11 13:20:51</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5736</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/11 10:01:04</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6024.1</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>6024.1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5736.1</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/11 10:00:59</t>
+          <t>10/12 14:15:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6024.1</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/11 13:20:51</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5736</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/11 10:01:04</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6250</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6024.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.1</t>
+          <t>6250</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/12 17:12:07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6250</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6250</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6250</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6250</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/12 14:15:13</t>
+          <t>10/13 12:17:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/12 17:12:07</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6250</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>12121.21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6250</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>12121.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/13 13:50:40</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12121.21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12121.21</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/13 12:17:22</t>
+          <t>10/14 10:48:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>27329.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/13 13:50:40</t>
+          <t>10/14 13:53:38</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>27329</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -242,7 +242,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
     </row>
@@ -254,7 +254,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>27329.19</t>
         </is>
       </c>
     </row>
@@ -266,7 +266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>27329</t>
         </is>
       </c>
     </row>
@@ -278,7 +278,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/14 10:48:43</t>
+          <t>10/15 11:12:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27329.19</t>
+          <t>23602.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/14 13:53:38</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>27329</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>190000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>23602.48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27329.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27329</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.19</t>
+          <t>23602.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 11:12:30</t>
+          <t>10/15 11:13:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23602.48</t>
+          <t>23456.79</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23602.48</t>
+          <t>23456.79</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23602.48</t>
+          <t>23456.79</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/15 11:33:25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/15 11:13:31</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>190000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>23456.79</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>190000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23456.79</t>
+          <t>490000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59601.37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>23456.79</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>59601.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 11:33:25</t>
+          <t>10/15 12:50:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10/15 11:33:25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>10/15 11:13:31</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>190000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>23456.79</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>490000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>59601.37</t>
+          <t>630000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76674.54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>59601.37</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>76674.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10/15 12:52:49</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>630000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>76674.54</t>
+          <t>630000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76674.54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>76674.54</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>16674.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 12:50:36</t>
+          <t>10/15 12:53:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/15 11:33:25</t>
+          <t>10/15 12:50:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,210 +159,252 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10/15 11:33:25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>10/15 11:13:31</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>190000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>23456.79</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>10/15 12:52:49</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>630000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>76674.54</t>
+          <t>730000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>88795.75</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>16674.54</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>28795.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -328,83 +328,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>10/15 14:12:19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>28795</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>10/15 12:52:49</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>730000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>88795.75</t>
+          <t>730000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>88795.75</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>88795</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>28795.75</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 12:53:42</t>
+          <t>10/16 11:16:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>117000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>14011.98</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,129 +114,53 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/15 12:50:36</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>140000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>17073.17</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/15 11:33:25</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>36144.58</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
+          <t>代付</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/15 11:13:31</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>190000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>费率</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>汇率</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23456.79</t>
+          <t>结算</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -244,7 +168,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>代付</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
@@ -261,30 +185,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>费率</t>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>汇率</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -294,144 +203,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>117000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/15 14:12:19</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>28795</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
+          <t>14011.98</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/15 12:52:49</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>60000</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>730000</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>88795.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>88795</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.75</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14011.98</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/16 12:33:18</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>37500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/16 11:16:33</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>117000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>14011.98</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>117000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14011.98</t>
+          <t>417000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51511.98</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>14011.98</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>51511.98</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/16 12:33:18</t>
+          <t>10/16 13:25:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>17575.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10/16 12:33:18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>37500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>10/16 11:16:33</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>117000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.35</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>14011.98</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>417000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>51511.98</t>
+          <t>562000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69087.73</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>51511.98</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>69087.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10/16 13:52:46</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>69087</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>562000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>69087.73</t>
+          <t>562000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69087.73</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>69087</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>69087.73</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/18 17:58:52</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>90000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>90000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10588.24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10588.24</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/18 16:49:54</t>
+          <t>10/19 11:00:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/18 17:58:52</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10588</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>12500</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10588</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.24</t>
+          <t>12500</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/19 13:54:28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>130000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15662.65</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/19 11:00:41</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>12500</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28162.65</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12500</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>28162.65</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/19 13:54:28</t>
+          <t>10/19 14:36:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>107700</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15662.65</t>
+          <t>12975.9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10/19 13:54:28</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>130000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>15662.65</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>10/19 11:00:41</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>12500</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>28162.65</t>
+          <t>337700</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41138.55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>28162.65</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>41138.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10/19 15:39:59</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>41138</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>337700</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>41138.55</t>
+          <t>337700</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41138.55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>41138</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>41138.55</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/20 14:15:42</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12345.68</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/20 13:41:54</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>160000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>260000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32345.68</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20000</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>32345.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/20 15:58:25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>32345</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>260000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32345.68</t>
+          <t>260000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32345.68</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>32345</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>32345.68</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/20 14:15:42</t>
+          <t>10/21 11:07:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>16829.27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/20 13:41:54</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/20 15:58:25</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>32345</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>16829.27</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32345.68</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>32345</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.68</t>
+          <t>16829.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/21 13:03:33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16829</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>138000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16829.27</t>
+          <t>138000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16829.27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16829</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>16829.27</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,210 +75,279 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/21 14:53:34</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>16867.47</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/21 11:07:19</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>138000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>16829.27</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/21 13:03:33</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/21 16:27:32</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>16867</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
-    </row>
+          <t>10/21 13:03:33</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>16829</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>16829.27</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>278000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>33696.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>33696</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.27</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.74</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/21 14:53:34</t>
+          <t>10/24 19:51:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16867.47</t>
+          <t>16167.66</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/21 11:07:19</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>16829.27</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/21 16:27:32</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>16867</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/21 13:03:33</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16829</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>135000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>16167.66</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>278000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>33696.74</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>33696</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.74</t>
+          <t>16167.66</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/24 21:54:50</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16167</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>135000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16167.66</t>
+          <t>135000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16167.66</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16167</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>16167.66</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.66</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/24 19:51:41</t>
+          <t>10/26 10:21:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16167.66</t>
+          <t>26993.87</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/24 21:54:50</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>16167</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>220000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>26993.87</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16167.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16167</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.66</t>
+          <t>26993.87</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/26 10:31:49</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>129840</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15643.37</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/26 10:21:34</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>220000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>26993.87</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>220000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26993.87</t>
+          <t>349840</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42637.24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>26993.87</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>42637.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/26 11:40:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>349840</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>42637.24</t>
+          <t>349840</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42637.24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>42637.24</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>41637.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 10:31:49</t>
+          <t>10/26 11:40:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>129840</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15643.37</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10/26 10:31:49</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>129840</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>15643.37</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>10/26 10:21:34</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>220000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>26993.87</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>10/26 11:40:01</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>349840</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>42637.24</t>
+          <t>649840</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>79447.05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>41637.24</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>78447.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>10/26 11:43:03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>10/26 11:40:01</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>649840</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>79447.05</t>
+          <t>649840</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>79447.05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>41000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>78447.05</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>38447.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 11:40:45</t>
+          <t>10/26 11:52:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/26 10:31:49</t>
+          <t>10/26 11:40:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>129840</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15643.37</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,237 +159,279 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10/26 10:31:49</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>129840</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15643.37</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>10/26 10:21:34</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>220000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>26993.87</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/26 11:43:03</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>10/26 11:43:03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>10/26 11:40:01</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>649840</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>79447.05</t>
+          <t>794840</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>97572.05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>41000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>38447.05</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>56572.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/26 10:31:49</t>
+          <t>10/26 10:21:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129840</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15643.37</t>
+          <t>26993.87</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -198,142 +198,127 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>10/26 10:21:34</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>220000</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>8.15</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>26993.87</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>10/26 11:43:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>标记人</t>
+          <t/>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>操作人</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/26 11:43:03</t>
+          <t>10/26 11:40:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -352,86 +337,59 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>10/26 11:40:01</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>665000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>794840</t>
+          <t>81928.68</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>97572.05</t>
+          <t>41000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>41000</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>56572.05</t>
+          <t>40928.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 11:52:27</t>
+          <t>10/26 13:25:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>128316</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>15459.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/26 11:40:45</t>
+          <t>10/26 11:52:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,237 +159,279 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10/26 11:40:45</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>36809.82</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>10/26 10:21:34</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>220000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>26993.87</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/26 11:43:03</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>10/26 11:43:03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>10/26 11:40:01</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>665000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>81928.68</t>
+          <t>793316</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>97388.44</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>41000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>40928.68</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>56388.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/26 11:43:03</t>
+          <t>10/26 13:27:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>56388</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -355,83 +355,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>10/26 11:43:03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>10/26 11:40:01</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>793316</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>97388.44</t>
+          <t>793316</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>97388.44</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>97388</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>56388.44</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/27 13:27:44</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/27 12:00:09</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>24539.88</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24539.88</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37039.88</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24539.88</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>37039.88</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/27 14:15:23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>37039</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>37039.88</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37039.88</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>37039</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>37039.88</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.88</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/27 13:27:44</t>
+          <t>10/28 13:17:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>15662.65</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/27 12:00:09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>24539.88</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/27 14:15:23</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>37039</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>130000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15662.65</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37039.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>37039</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.88</t>
+          <t>15662.65</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/28 15:05:50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>136000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/28 13:17:59</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>130000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>15662.65</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15662.65</t>
+          <t>266000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32662.65</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15662.65</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>32662.65</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/28 16:19:30</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>32662</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>266000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32662.65</t>
+          <t>266000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32662.65</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>32662</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>32662.65</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.65</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/28 15:05:50</t>
+          <t>10/29 12:57:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>136000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>24691.36</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/28 13:17:59</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>15662.65</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/28 16:19:30</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>32662</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>24691.36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32662.65</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>32662</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.65</t>
+          <t>24691.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/29 15:21:37</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>24691</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24691.36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>24691</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24691.36</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/29 19:47:35</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>301700</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36131.74</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/29 12:57:11</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>24691.36</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/29 15:21:37</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>24691</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>501700</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24691</t>
+          <t>60823.09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>24691</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.36</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>36132.09</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>10/29 21:17:42</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>36132</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>10/29 15:21:37</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>24691</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>501700</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>60823.09</t>
+          <t>501700</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24691</t>
+          <t>60823.09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>60823</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>36132.09</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.09</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/29 19:47:35</t>
+          <t>10/31 11:20:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>301700</t>
+          <t>157700</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36131.74</t>
+          <t>18886.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/29 12:57:11</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>24691.36</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/29 21:17:42</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>36132</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/29 15:21:37</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24691</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>157700</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>18886.23</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>501700</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>60823.09</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>60823</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.09</t>
+          <t>18886.23</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/31 11:20:06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>157700</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18886.23</t>
+          <t>157700</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18886.23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>18886.23</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17886.23</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10/31 14:59:34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17886</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/31 11:20:06</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>157700</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18886.23</t>
+          <t>157700</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>18886.23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>18886</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>17886.23</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.23</t>
         </is>
       </c>
     </row>
